--- a/station.xlsx
+++ b/station.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\eltai_a\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08D3011A-7278-497E-96D5-83D59092BE74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{585E808E-BB84-434D-A549-567865D59BB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14373" yWindow="14" windowWidth="20703" windowHeight="18828" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="489" yWindow="0" windowWidth="22959" windowHeight="18829" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3768" uniqueCount="2713">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4126" uniqueCount="2759">
   <si>
     <t>Станция/пост</t>
   </si>
@@ -8249,17 +8249,163 @@
   <si>
     <t>Агрометеорология</t>
   </si>
+  <si>
+    <t>ПНЗ №7</t>
+  </si>
+  <si>
+    <t>ПНЗ №9</t>
+  </si>
+  <si>
+    <t>ПНЗ №8</t>
+  </si>
+  <si>
+    <t>ПНЗ №10</t>
+  </si>
+  <si>
+    <t>ПНЗ №6</t>
+  </si>
+  <si>
+    <t>ПНЗ №2</t>
+  </si>
+  <si>
+    <t>ПНЗ №1</t>
+  </si>
+  <si>
+    <t>ПНЗ №3</t>
+  </si>
+  <si>
+    <t>ПНЗ №4</t>
+  </si>
+  <si>
+    <t>ПНЗ №5</t>
+  </si>
+  <si>
+    <t>Экология</t>
+  </si>
+  <si>
+    <t>ПНЗ №29</t>
+  </si>
+  <si>
+    <t>ПНЗ №31</t>
+  </si>
+  <si>
+    <t>ПНЗ №30</t>
+  </si>
+  <si>
+    <t>ПНЗ №27</t>
+  </si>
+  <si>
+    <t>ПНЗ№3</t>
+  </si>
+  <si>
+    <t>ПНЗ№6</t>
+  </si>
+  <si>
+    <t>ПНЗ№5</t>
+  </si>
+  <si>
+    <t>ПНЗ№28</t>
+  </si>
+  <si>
+    <t>ПНЗ№1</t>
+  </si>
+  <si>
+    <t>ПНЗ№12</t>
+  </si>
+  <si>
+    <t>ПНЗ№16</t>
+  </si>
+  <si>
+    <t>ПНЗ№25</t>
+  </si>
+  <si>
+    <t>ПНЗ№26</t>
+  </si>
+  <si>
+    <t>ПНЗ №5 (г. Щучинск)</t>
+  </si>
+  <si>
+    <t>ПНЗ№2 (п. Бурабай)</t>
+  </si>
+  <si>
+    <t>ПНЗ№2</t>
+  </si>
+  <si>
+    <t>ПНЗ№8</t>
+  </si>
+  <si>
+    <t>ПНЗ№9</t>
+  </si>
+  <si>
+    <t>ПНЗ№11</t>
+  </si>
+  <si>
+    <t>ПНЗ№17</t>
+  </si>
+  <si>
+    <t>ПНЗ№7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.953111° </t>
+  </si>
+  <si>
+    <t>51.735194°</t>
+  </si>
+  <si>
+    <t>47.094444°</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 51.891361°</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.083333° </t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.9° </t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.133333° </t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.866667° </t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.933333° </t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.983333° </t>
+  </si>
+  <si>
+    <t>ПНЗ №12</t>
+  </si>
+  <si>
+    <t>ПНЗ №11</t>
+  </si>
+  <si>
+    <t>ПНЗ№4</t>
+  </si>
+  <si>
+    <t>ПНЗ№13</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -8454,109 +8600,110 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -8837,7 +8984,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E1016"/>
+  <dimension ref="A1:E1190"/>
   <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="26.875" customWidth="1"/>
@@ -10665,7 +10812,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="108" spans="1:5" ht="28.55" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A108">
         <v>107</v>
       </c>
@@ -10682,7 +10829,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="109" spans="1:5" ht="28.55" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A109">
         <v>108</v>
       </c>
@@ -10699,7 +10846,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="110" spans="1:5" ht="28.55" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A110">
         <v>109</v>
       </c>
@@ -10716,7 +10863,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="111" spans="1:5" ht="42.8" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A111">
         <v>110</v>
       </c>
@@ -10733,7 +10880,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="112" spans="1:5" ht="42.8" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A112">
         <v>111</v>
       </c>
@@ -10750,7 +10897,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="113" spans="1:5" ht="42.8" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A113">
         <v>112</v>
       </c>
@@ -10767,7 +10914,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="114" spans="1:5" ht="42.8" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A114">
         <v>113</v>
       </c>
@@ -10784,7 +10931,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="115" spans="1:5" ht="42.8" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:5" ht="28.55" x14ac:dyDescent="0.25">
       <c r="A115">
         <v>114</v>
       </c>
@@ -10801,7 +10948,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="116" spans="1:5" ht="42.8" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:5" ht="28.55" x14ac:dyDescent="0.25">
       <c r="A116">
         <v>115</v>
       </c>
@@ -10818,7 +10965,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="117" spans="1:5" ht="42.8" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:5" ht="28.55" x14ac:dyDescent="0.25">
       <c r="A117">
         <v>116</v>
       </c>
@@ -10835,7 +10982,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="118" spans="1:5" ht="42.8" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:5" ht="28.55" x14ac:dyDescent="0.25">
       <c r="A118">
         <v>117</v>
       </c>
@@ -26113,6 +26260,2964 @@
       </c>
       <c r="E1016" t="s">
         <v>2712</v>
+      </c>
+    </row>
+    <row r="1017" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1017">
+        <v>1016</v>
+      </c>
+      <c r="B1017" s="38" t="s">
+        <v>2713</v>
+      </c>
+      <c r="C1017" s="38">
+        <v>71.430773000000002</v>
+      </c>
+      <c r="D1017" s="38">
+        <v>51.118684000000002</v>
+      </c>
+      <c r="E1017" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="1018" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1018">
+        <v>1017</v>
+      </c>
+      <c r="B1018" s="38" t="s">
+        <v>2714</v>
+      </c>
+      <c r="C1018" s="38">
+        <v>71.484431388888893</v>
+      </c>
+      <c r="D1018" s="38">
+        <v>51.123244722222204</v>
+      </c>
+      <c r="E1018" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="1019" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1019">
+        <v>1018</v>
+      </c>
+      <c r="B1019" s="38" t="s">
+        <v>2715</v>
+      </c>
+      <c r="C1019" s="38">
+        <v>71.345104444444402</v>
+      </c>
+      <c r="D1019" s="38">
+        <v>51.185364722222197</v>
+      </c>
+      <c r="E1019" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="1020" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1020">
+        <v>1019</v>
+      </c>
+      <c r="B1020" s="38" t="s">
+        <v>2716</v>
+      </c>
+      <c r="C1020" s="38">
+        <v>71.472398055555601</v>
+      </c>
+      <c r="D1020" s="38">
+        <v>51.157116666666703</v>
+      </c>
+      <c r="E1020" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="1021" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1021">
+        <v>1020</v>
+      </c>
+      <c r="B1021" s="38" t="s">
+        <v>2717</v>
+      </c>
+      <c r="C1021" s="38">
+        <v>71.487347999999997</v>
+      </c>
+      <c r="D1021" s="38">
+        <v>51.172759999999997</v>
+      </c>
+      <c r="E1021" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="1022" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1022">
+        <v>1021</v>
+      </c>
+      <c r="B1022" s="38" t="s">
+        <v>2718</v>
+      </c>
+      <c r="C1022" s="38">
+        <v>71.424052000000003</v>
+      </c>
+      <c r="D1022" s="38">
+        <v>51.170541</v>
+      </c>
+      <c r="E1022" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="1023" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1023">
+        <v>1022</v>
+      </c>
+      <c r="B1023" s="38" t="s">
+        <v>2719</v>
+      </c>
+      <c r="C1023" s="38">
+        <v>71.394573611111099</v>
+      </c>
+      <c r="D1023" s="38">
+        <v>51.171116388888898</v>
+      </c>
+      <c r="E1023" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="1024" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1024">
+        <v>1023</v>
+      </c>
+      <c r="B1024" s="38" t="s">
+        <v>2720</v>
+      </c>
+      <c r="C1024" s="38">
+        <v>71.432912000000002</v>
+      </c>
+      <c r="D1024" s="38">
+        <v>51.196033999999997</v>
+      </c>
+      <c r="E1024" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="1025" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1025">
+        <v>1024</v>
+      </c>
+      <c r="B1025" s="38" t="s">
+        <v>2721</v>
+      </c>
+      <c r="C1025" s="38">
+        <v>71.525903999999997</v>
+      </c>
+      <c r="D1025" s="38">
+        <v>51.148389999999999</v>
+      </c>
+      <c r="E1025" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="1026" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1026">
+        <v>1025</v>
+      </c>
+      <c r="B1026" s="38" t="s">
+        <v>2722</v>
+      </c>
+      <c r="C1026" s="38">
+        <v>71.414702000000005</v>
+      </c>
+      <c r="D1026" s="38">
+        <v>51.157933</v>
+      </c>
+      <c r="E1026" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="1027" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1027">
+        <v>1026</v>
+      </c>
+      <c r="B1027" s="38" t="s">
+        <v>2718</v>
+      </c>
+      <c r="C1027" s="38">
+        <v>76.875983000000005</v>
+      </c>
+      <c r="D1027" s="38">
+        <v>43.356909000000002</v>
+      </c>
+      <c r="E1027" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="1028" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1028">
+        <v>1027</v>
+      </c>
+      <c r="B1028" s="38" t="s">
+        <v>2724</v>
+      </c>
+      <c r="C1028" s="38">
+        <v>76.952190277777802</v>
+      </c>
+      <c r="D1028" s="38">
+        <v>43.337288888888899</v>
+      </c>
+      <c r="E1028" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="1029" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1029">
+        <v>1028</v>
+      </c>
+      <c r="B1029" s="38" t="s">
+        <v>2725</v>
+      </c>
+      <c r="C1029" s="38">
+        <v>76.889592777777807</v>
+      </c>
+      <c r="D1029" s="38">
+        <v>43.1801552777778</v>
+      </c>
+      <c r="E1029" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="1030" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1030">
+        <v>1029</v>
+      </c>
+      <c r="B1030" s="38" t="s">
+        <v>2726</v>
+      </c>
+      <c r="C1030" s="38">
+        <v>76.851363000000006</v>
+      </c>
+      <c r="D1030" s="38">
+        <v>43.298772</v>
+      </c>
+      <c r="E1030" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="1031" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1031">
+        <v>1030</v>
+      </c>
+      <c r="B1031" s="38" t="s">
+        <v>2727</v>
+      </c>
+      <c r="C1031" s="38">
+        <v>76.844007000000005</v>
+      </c>
+      <c r="D1031" s="38">
+        <v>43.271427000000003</v>
+      </c>
+      <c r="E1031" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="1032" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1032">
+        <v>1031</v>
+      </c>
+      <c r="B1032" s="38" t="s">
+        <v>2719</v>
+      </c>
+      <c r="C1032" s="38">
+        <v>76.926400999999998</v>
+      </c>
+      <c r="D1032" s="38">
+        <v>43.220247000000001</v>
+      </c>
+      <c r="E1032" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="1033" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1033">
+        <v>1032</v>
+      </c>
+      <c r="B1033" s="38" t="s">
+        <v>2721</v>
+      </c>
+      <c r="C1033" s="38">
+        <v>76.992745999999997</v>
+      </c>
+      <c r="D1033" s="38">
+        <v>43.374209</v>
+      </c>
+      <c r="E1033" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="1034" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1034">
+        <v>1033</v>
+      </c>
+      <c r="B1034" s="38" t="s">
+        <v>2728</v>
+      </c>
+      <c r="C1034" s="38">
+        <v>76.816496000000001</v>
+      </c>
+      <c r="D1034" s="38">
+        <v>43.258318000000003</v>
+      </c>
+      <c r="E1034" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="1035" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1035">
+        <v>1034</v>
+      </c>
+      <c r="B1035" s="38" t="s">
+        <v>2729</v>
+      </c>
+      <c r="C1035" s="38">
+        <v>76.925926000000004</v>
+      </c>
+      <c r="D1035" s="38">
+        <v>43.300730000000001</v>
+      </c>
+      <c r="E1035" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="1036" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1036">
+        <v>1035</v>
+      </c>
+      <c r="B1036" s="38" t="s">
+        <v>2730</v>
+      </c>
+      <c r="C1036" s="38">
+        <v>76.991245000000006</v>
+      </c>
+      <c r="D1036" s="38">
+        <v>43.288601</v>
+      </c>
+      <c r="E1036" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="1037" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1037">
+        <v>1036</v>
+      </c>
+      <c r="B1037" s="38" t="s">
+        <v>2731</v>
+      </c>
+      <c r="C1037" s="38">
+        <v>77.004807999999997</v>
+      </c>
+      <c r="D1037" s="38">
+        <v>43.36374</v>
+      </c>
+      <c r="E1037" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="1038" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1038">
+        <v>1037</v>
+      </c>
+      <c r="B1038" s="38" t="s">
+        <v>2732</v>
+      </c>
+      <c r="C1038" s="38">
+        <v>76.933418333333293</v>
+      </c>
+      <c r="D1038" s="38">
+        <v>43.237947499999997</v>
+      </c>
+      <c r="E1038" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="1039" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1039">
+        <v>1038</v>
+      </c>
+      <c r="B1039" s="38" t="s">
+        <v>2733</v>
+      </c>
+      <c r="C1039" s="38">
+        <v>76.934279166666698</v>
+      </c>
+      <c r="D1039" s="38">
+        <v>43.269433888888898</v>
+      </c>
+      <c r="E1039" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="1040" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1040">
+        <v>1039</v>
+      </c>
+      <c r="B1040" s="38" t="s">
+        <v>2734</v>
+      </c>
+      <c r="C1040" s="38">
+        <v>76.920516111111098</v>
+      </c>
+      <c r="D1040" s="38">
+        <v>43.323973333333299</v>
+      </c>
+      <c r="E1040" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="1041" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1041">
+        <v>1040</v>
+      </c>
+      <c r="B1041" s="38" t="s">
+        <v>2735</v>
+      </c>
+      <c r="C1041" s="38">
+        <v>76.832467500000007</v>
+      </c>
+      <c r="D1041" s="38">
+        <v>43.232702777777803</v>
+      </c>
+      <c r="E1041" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="1042" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1042">
+        <v>1041</v>
+      </c>
+      <c r="B1042" s="38" t="s">
+        <v>2736</v>
+      </c>
+      <c r="C1042" s="38">
+        <v>76.875524166666693</v>
+      </c>
+      <c r="D1042" s="38">
+        <v>43.250291388888897</v>
+      </c>
+      <c r="E1042" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="1043" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1043">
+        <v>1042</v>
+      </c>
+      <c r="B1043" s="38" t="s">
+        <v>2737</v>
+      </c>
+      <c r="C1043" s="38">
+        <v>70.250620999999995</v>
+      </c>
+      <c r="D1043" s="38">
+        <v>52.951922000000003</v>
+      </c>
+      <c r="E1043" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="1044" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1044">
+        <v>1043</v>
+      </c>
+      <c r="B1044" s="38" t="s">
+        <v>2738</v>
+      </c>
+      <c r="C1044" s="38">
+        <v>70.302069000000003</v>
+      </c>
+      <c r="D1044" s="38">
+        <v>53.085628999999997</v>
+      </c>
+      <c r="E1044" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="1045" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1045">
+        <v>1044</v>
+      </c>
+      <c r="B1045" s="38" t="s">
+        <v>2732</v>
+      </c>
+      <c r="C1045" s="38">
+        <v>70.609943999999999</v>
+      </c>
+      <c r="D1045" s="38">
+        <v>53.002194000000003</v>
+      </c>
+      <c r="E1045" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="1046" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1046">
+        <v>1045</v>
+      </c>
+      <c r="B1046" s="38" t="s">
+        <v>2719</v>
+      </c>
+      <c r="C1046" s="38">
+        <v>68.346593999999996</v>
+      </c>
+      <c r="D1046" s="38">
+        <v>51.818880999999998</v>
+      </c>
+      <c r="E1046" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="1047" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1047">
+        <v>1046</v>
+      </c>
+      <c r="B1047" s="38" t="s">
+        <v>2728</v>
+      </c>
+      <c r="C1047" s="38">
+        <v>71.939444440000003</v>
+      </c>
+      <c r="D1047" s="38">
+        <v>52.43936111</v>
+      </c>
+      <c r="E1047" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="1048" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1048">
+        <v>1047</v>
+      </c>
+      <c r="B1048" s="38" t="s">
+        <v>2739</v>
+      </c>
+      <c r="C1048" s="38">
+        <v>69.425588000000005</v>
+      </c>
+      <c r="D1048" s="38">
+        <v>53.283029999999997</v>
+      </c>
+      <c r="E1048" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="1049" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1049">
+        <v>1048</v>
+      </c>
+      <c r="B1049" s="38" t="s">
+        <v>2732</v>
+      </c>
+      <c r="C1049" s="38">
+        <v>69.650000000000006</v>
+      </c>
+      <c r="D1049" s="38">
+        <v>53.534213889999997</v>
+      </c>
+      <c r="E1049" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="1050" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1050">
+        <v>1049</v>
+      </c>
+      <c r="B1050" s="38" t="s">
+        <v>2732</v>
+      </c>
+      <c r="C1050" s="38">
+        <v>71.868089999999995</v>
+      </c>
+      <c r="D1050" s="38">
+        <v>52.340102000000002</v>
+      </c>
+      <c r="E1050" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="1051" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1051">
+        <v>1050</v>
+      </c>
+      <c r="B1051" s="38" t="s">
+        <v>2739</v>
+      </c>
+      <c r="C1051" s="38">
+        <v>78.344825</v>
+      </c>
+      <c r="D1051" s="38">
+        <v>45.004358000000003</v>
+      </c>
+      <c r="E1051" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="1052" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1052">
+        <v>1051</v>
+      </c>
+      <c r="B1052" s="38" t="s">
+        <v>2732</v>
+      </c>
+      <c r="C1052" s="38">
+        <v>78.360650277777793</v>
+      </c>
+      <c r="D1052" s="38">
+        <v>45.0069466666667</v>
+      </c>
+      <c r="E1052" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="1053" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1053">
+        <v>1052</v>
+      </c>
+      <c r="B1053" s="38" t="s">
+        <v>2719</v>
+      </c>
+      <c r="C1053" s="38">
+        <v>79.990333000000007</v>
+      </c>
+      <c r="D1053" s="38">
+        <v>44.153528000000001</v>
+      </c>
+      <c r="E1053" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="1054" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1054">
+        <v>1053</v>
+      </c>
+      <c r="B1054" s="38" t="s">
+        <v>2719</v>
+      </c>
+      <c r="C1054" s="38">
+        <v>77.239166999999995</v>
+      </c>
+      <c r="D1054" s="38">
+        <v>43.302222</v>
+      </c>
+      <c r="E1054" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="1055" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1055">
+        <v>1054</v>
+      </c>
+      <c r="B1055" s="38" t="s">
+        <v>2718</v>
+      </c>
+      <c r="C1055" s="38">
+        <v>57.126159000000001</v>
+      </c>
+      <c r="D1055" s="38">
+        <v>50.316025000000003</v>
+      </c>
+      <c r="E1055" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="1056" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1056">
+        <v>1055</v>
+      </c>
+      <c r="B1056" s="38" t="s">
+        <v>2720</v>
+      </c>
+      <c r="C1056" s="38">
+        <v>57.168751999999998</v>
+      </c>
+      <c r="D1056" s="38">
+        <v>50.294316999999999</v>
+      </c>
+      <c r="E1056" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="1057" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1057">
+        <v>1056</v>
+      </c>
+      <c r="B1057" s="38" t="s">
+        <v>2717</v>
+      </c>
+      <c r="C1057" s="38">
+        <v>57.222090000000001</v>
+      </c>
+      <c r="D1057" s="38">
+        <v>50.29034</v>
+      </c>
+      <c r="E1057" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="1058" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1058">
+        <v>1057</v>
+      </c>
+      <c r="B1058" s="38" t="s">
+        <v>2719</v>
+      </c>
+      <c r="C1058" s="38">
+        <v>57.223519000000003</v>
+      </c>
+      <c r="D1058" s="38">
+        <v>50.258119999999998</v>
+      </c>
+      <c r="E1058" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="1059" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1059">
+        <v>1058</v>
+      </c>
+      <c r="B1059" s="38" t="s">
+        <v>2721</v>
+      </c>
+      <c r="C1059" s="38">
+        <v>57.141717</v>
+      </c>
+      <c r="D1059" s="38">
+        <v>50.317881</v>
+      </c>
+      <c r="E1059" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="1060" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1060">
+        <v>1059</v>
+      </c>
+      <c r="B1060" s="38" t="s">
+        <v>2722</v>
+      </c>
+      <c r="C1060" s="38">
+        <v>57.214084</v>
+      </c>
+      <c r="D1060" s="38">
+        <v>50.283495000000002</v>
+      </c>
+      <c r="E1060" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="1061" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1061">
+        <v>1060</v>
+      </c>
+      <c r="B1061" s="38" t="s">
+        <v>2719</v>
+      </c>
+      <c r="C1061" s="38">
+        <v>58.436750000000004</v>
+      </c>
+      <c r="D1061" s="38">
+        <v>50.249721999999998</v>
+      </c>
+      <c r="E1061" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="1062" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1062">
+        <v>1061</v>
+      </c>
+      <c r="B1062" s="38" t="s">
+        <v>2719</v>
+      </c>
+      <c r="C1062" s="38">
+        <v>57.422832999999997</v>
+      </c>
+      <c r="D1062" s="38">
+        <v>49.471693999999999</v>
+      </c>
+      <c r="E1062" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="1063" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1063">
+        <v>1062</v>
+      </c>
+      <c r="B1063" s="38" t="s">
+        <v>2719</v>
+      </c>
+      <c r="C1063" s="38">
+        <v>57.178694</v>
+      </c>
+      <c r="D1063" s="38">
+        <v>48.579917000000002</v>
+      </c>
+      <c r="E1063" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="1064" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1064">
+        <v>1063</v>
+      </c>
+      <c r="B1064" s="38" t="s">
+        <v>2719</v>
+      </c>
+      <c r="C1064" s="38">
+        <v>57.116667</v>
+      </c>
+      <c r="D1064" s="38">
+        <v>48.604971999999997</v>
+      </c>
+      <c r="E1064" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="1065" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1065">
+        <v>1064</v>
+      </c>
+      <c r="B1065" s="38" t="s">
+        <v>2740</v>
+      </c>
+      <c r="C1065" s="38">
+        <v>51.941388889999999</v>
+      </c>
+      <c r="D1065" s="38">
+        <v>47.09639722</v>
+      </c>
+      <c r="E1065" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="1066" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1066">
+        <v>1065</v>
+      </c>
+      <c r="B1066" s="38" t="s">
+        <v>2741</v>
+      </c>
+      <c r="C1066" s="38">
+        <v>51.964852999999998</v>
+      </c>
+      <c r="D1066" s="38">
+        <v>47.139398999999997</v>
+      </c>
+      <c r="E1066" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="1067" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1067">
+        <v>1066</v>
+      </c>
+      <c r="B1067" s="38" t="s">
+        <v>2729</v>
+      </c>
+      <c r="C1067" s="38">
+        <v>51.981453000000002</v>
+      </c>
+      <c r="D1067" s="38">
+        <v>47.155836000000001</v>
+      </c>
+      <c r="E1067" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="1068" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1068">
+        <v>1067</v>
+      </c>
+      <c r="B1068" s="38" t="s">
+        <v>2742</v>
+      </c>
+      <c r="C1068" s="38" t="s">
+        <v>2745</v>
+      </c>
+      <c r="D1068" s="38" t="s">
+        <v>2746</v>
+      </c>
+      <c r="E1068" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="1069" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1069">
+        <v>1068</v>
+      </c>
+      <c r="B1069" s="38" t="s">
+        <v>2733</v>
+      </c>
+      <c r="C1069" s="38" t="s">
+        <v>2747</v>
+      </c>
+      <c r="D1069" s="38" t="s">
+        <v>2748</v>
+      </c>
+      <c r="E1069" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="1070" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1070">
+        <v>1069</v>
+      </c>
+      <c r="B1070" s="38" t="s">
+        <v>2730</v>
+      </c>
+      <c r="C1070" s="38" t="s">
+        <v>2749</v>
+      </c>
+      <c r="D1070" s="38" t="s">
+        <v>2750</v>
+      </c>
+      <c r="E1070" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="1071" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1071">
+        <v>1070</v>
+      </c>
+      <c r="B1071" s="38" t="s">
+        <v>2743</v>
+      </c>
+      <c r="C1071" s="38" t="s">
+        <v>2751</v>
+      </c>
+      <c r="D1071" s="38" t="s">
+        <v>2752</v>
+      </c>
+      <c r="E1071" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="1072" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1072">
+        <v>1071</v>
+      </c>
+      <c r="B1072" s="38" t="s">
+        <v>2732</v>
+      </c>
+      <c r="C1072" s="38">
+        <v>51.870885999999999</v>
+      </c>
+      <c r="D1072" s="38">
+        <v>47.126122000000002</v>
+      </c>
+      <c r="E1072" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="1073" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1073">
+        <v>1072</v>
+      </c>
+      <c r="B1073" s="38" t="s">
+        <v>2730</v>
+      </c>
+      <c r="C1073" s="38">
+        <v>51.886425000000003</v>
+      </c>
+      <c r="D1073" s="38">
+        <v>47.066847000000003</v>
+      </c>
+      <c r="E1073" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="1074" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1074">
+        <v>1073</v>
+      </c>
+      <c r="B1074" s="38" t="s">
+        <v>2744</v>
+      </c>
+      <c r="C1074" s="38">
+        <v>54.011666669999997</v>
+      </c>
+      <c r="D1074" s="38">
+        <v>46.960619440000002</v>
+      </c>
+      <c r="E1074" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="1075" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1075">
+        <v>1074</v>
+      </c>
+      <c r="B1075" s="38" t="s">
+        <v>2744</v>
+      </c>
+      <c r="C1075" s="38" t="s">
+        <v>2753</v>
+      </c>
+      <c r="D1075" s="38" t="s">
+        <v>2754</v>
+      </c>
+      <c r="E1075" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="1076" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1076">
+        <v>1075</v>
+      </c>
+      <c r="B1076" s="38" t="s">
+        <v>2719</v>
+      </c>
+      <c r="C1076" s="38">
+        <v>50.804833000000002</v>
+      </c>
+      <c r="D1076" s="38">
+        <v>47.049222</v>
+      </c>
+      <c r="E1076" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="1077" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1077">
+        <v>1076</v>
+      </c>
+      <c r="B1077" s="38" t="s">
+        <v>2719</v>
+      </c>
+      <c r="C1077" s="38">
+        <v>53.332250000000002</v>
+      </c>
+      <c r="D1077" s="38">
+        <v>47.645055999999997</v>
+      </c>
+      <c r="E1077" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="1078" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1078">
+        <v>1077</v>
+      </c>
+      <c r="B1078" s="38" t="s">
+        <v>2719</v>
+      </c>
+      <c r="C1078" s="38">
+        <v>51.735083000000003</v>
+      </c>
+      <c r="D1078" s="38">
+        <v>48.555999999999997</v>
+      </c>
+      <c r="E1078" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="1079" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1079">
+        <v>1078</v>
+      </c>
+      <c r="B1079" s="38" t="s">
+        <v>2719</v>
+      </c>
+      <c r="C1079" s="38">
+        <v>49.270611000000002</v>
+      </c>
+      <c r="D1079" s="38">
+        <v>46.602722</v>
+      </c>
+      <c r="E1079" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="1080" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1080">
+        <v>1079</v>
+      </c>
+      <c r="B1080" s="38" t="s">
+        <v>2719</v>
+      </c>
+      <c r="C1080" s="38">
+        <v>80.249200000000002</v>
+      </c>
+      <c r="D1080" s="38">
+        <v>50.414299999999997</v>
+      </c>
+      <c r="E1080" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="1081" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1081">
+        <v>1080</v>
+      </c>
+      <c r="B1081" s="38" t="s">
+        <v>2718</v>
+      </c>
+      <c r="C1081" s="38">
+        <v>80.201238000000004</v>
+      </c>
+      <c r="D1081" s="38">
+        <v>50.399177000000002</v>
+      </c>
+      <c r="E1081" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="1082" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1082">
+        <v>1081</v>
+      </c>
+      <c r="B1082" s="38" t="s">
+        <v>2721</v>
+      </c>
+      <c r="C1082" s="38">
+        <v>80.240877999999995</v>
+      </c>
+      <c r="D1082" s="38">
+        <v>50.437553999999999</v>
+      </c>
+      <c r="E1082" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="1083" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1083">
+        <v>1082</v>
+      </c>
+      <c r="B1083" s="38" t="s">
+        <v>2720</v>
+      </c>
+      <c r="C1083" s="38">
+        <v>80.274279000000007</v>
+      </c>
+      <c r="D1083" s="38">
+        <v>50.420211999999999</v>
+      </c>
+      <c r="E1083" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="1084" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1084">
+        <v>1083</v>
+      </c>
+      <c r="B1084" s="38" t="s">
+        <v>2720</v>
+      </c>
+      <c r="C1084" s="38">
+        <v>82.312595000000002</v>
+      </c>
+      <c r="D1084" s="38">
+        <v>50.147264999999997</v>
+      </c>
+      <c r="E1084" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="1085" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1085">
+        <v>1084</v>
+      </c>
+      <c r="B1085" s="38" t="s">
+        <v>2719</v>
+      </c>
+      <c r="C1085" s="38">
+        <v>82.310556666666699</v>
+      </c>
+      <c r="D1085" s="38">
+        <v>50.139375555555603</v>
+      </c>
+      <c r="E1085" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="1086" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1086">
+        <v>1085</v>
+      </c>
+      <c r="B1086" s="38" t="s">
+        <v>2720</v>
+      </c>
+      <c r="C1086" s="38">
+        <v>82.365762000000004</v>
+      </c>
+      <c r="D1086" s="38">
+        <v>49.575944</v>
+      </c>
+      <c r="E1086" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="1087" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1087">
+        <v>1086</v>
+      </c>
+      <c r="B1087" s="38" t="s">
+        <v>2718</v>
+      </c>
+      <c r="C1087" s="38">
+        <v>82.391154</v>
+      </c>
+      <c r="D1087" s="38">
+        <v>49.564081000000002</v>
+      </c>
+      <c r="E1087" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="1088" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1088">
+        <v>1087</v>
+      </c>
+      <c r="B1088" s="38" t="s">
+        <v>2719</v>
+      </c>
+      <c r="C1088" s="38">
+        <v>82.361996000000005</v>
+      </c>
+      <c r="D1088" s="38">
+        <v>49.584104000000004</v>
+      </c>
+      <c r="E1088" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="1089" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1089">
+        <v>1088</v>
+      </c>
+      <c r="B1089" s="38" t="s">
+        <v>2722</v>
+      </c>
+      <c r="C1089" s="38">
+        <v>82.372902999999994</v>
+      </c>
+      <c r="D1089" s="38">
+        <v>49.564658999999999</v>
+      </c>
+      <c r="E1089" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="1090" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1090">
+        <v>1089</v>
+      </c>
+      <c r="B1090" s="38" t="s">
+        <v>2713</v>
+      </c>
+      <c r="C1090" s="38">
+        <v>82.565565000000007</v>
+      </c>
+      <c r="D1090" s="38">
+        <v>50.009288055555601</v>
+      </c>
+      <c r="E1090" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="1091" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1091">
+        <v>1090</v>
+      </c>
+      <c r="B1091" s="38" t="s">
+        <v>2715</v>
+      </c>
+      <c r="C1091" s="38">
+        <v>82.739706944444507</v>
+      </c>
+      <c r="D1091" s="38">
+        <v>50.027921111111098</v>
+      </c>
+      <c r="E1091" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="1092" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1092">
+        <v>1091</v>
+      </c>
+      <c r="B1092" s="38" t="s">
+        <v>2755</v>
+      </c>
+      <c r="C1092" s="38">
+        <v>82.622988611111097</v>
+      </c>
+      <c r="D1092" s="38">
+        <v>49.900071944444399</v>
+      </c>
+      <c r="E1092" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="1093" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1093">
+        <v>1092</v>
+      </c>
+      <c r="B1093" s="38" t="s">
+        <v>2721</v>
+      </c>
+      <c r="C1093" s="38">
+        <v>82.635582999999997</v>
+      </c>
+      <c r="D1093" s="38">
+        <v>49.978389</v>
+      </c>
+      <c r="E1093" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="1094" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1094">
+        <v>1093</v>
+      </c>
+      <c r="B1094" s="38" t="s">
+        <v>2717</v>
+      </c>
+      <c r="C1094" s="38">
+        <v>82.571360999999996</v>
+      </c>
+      <c r="D1094" s="38">
+        <v>49.982166999999997</v>
+      </c>
+      <c r="E1094" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="1095" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1095">
+        <v>1094</v>
+      </c>
+      <c r="B1095" s="38" t="s">
+        <v>2756</v>
+      </c>
+      <c r="C1095" s="38">
+        <v>82.605610999999996</v>
+      </c>
+      <c r="D1095" s="38">
+        <v>49.900888999999999</v>
+      </c>
+      <c r="E1095" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="1096" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1096">
+        <v>1095</v>
+      </c>
+      <c r="B1096" s="38" t="s">
+        <v>2720</v>
+      </c>
+      <c r="C1096" s="38">
+        <v>83.5</v>
+      </c>
+      <c r="D1096" s="38">
+        <v>50.329999722222198</v>
+      </c>
+      <c r="E1096" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="1097" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1097">
+        <v>1096</v>
+      </c>
+      <c r="B1097" s="38" t="s">
+        <v>2719</v>
+      </c>
+      <c r="C1097" s="38">
+        <v>83.450678055555599</v>
+      </c>
+      <c r="D1097" s="38">
+        <v>50.3273941666667</v>
+      </c>
+      <c r="E1097" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="1098" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1098">
+        <v>1097</v>
+      </c>
+      <c r="B1098" s="38" t="s">
+        <v>2717</v>
+      </c>
+      <c r="C1098" s="38">
+        <v>83.502336944444394</v>
+      </c>
+      <c r="D1098" s="38">
+        <v>50.3374061111111</v>
+      </c>
+      <c r="E1098" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="1099" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1099">
+        <v>1098</v>
+      </c>
+      <c r="B1099" s="38" t="s">
+        <v>2732</v>
+      </c>
+      <c r="C1099" s="38">
+        <v>84.271231999999998</v>
+      </c>
+      <c r="D1099" s="38">
+        <v>49.727654999999999</v>
+      </c>
+      <c r="E1099" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="1100" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1100">
+        <v>1099</v>
+      </c>
+      <c r="B1100" s="38" t="s">
+        <v>2719</v>
+      </c>
+      <c r="C1100" s="38">
+        <v>80.437360999999996</v>
+      </c>
+      <c r="D1100" s="38">
+        <v>47.965389000000002</v>
+      </c>
+      <c r="E1100" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="1101" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1101">
+        <v>1100</v>
+      </c>
+      <c r="B1101" s="38" t="s">
+        <v>2719</v>
+      </c>
+      <c r="C1101" s="38">
+        <v>81.573250000000002</v>
+      </c>
+      <c r="D1101" s="38">
+        <v>49.708666999999998</v>
+      </c>
+      <c r="E1101" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="1102" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1102">
+        <v>1101</v>
+      </c>
+      <c r="B1102" s="38" t="s">
+        <v>2719</v>
+      </c>
+      <c r="C1102" s="38">
+        <v>81.918278000000001</v>
+      </c>
+      <c r="D1102" s="38">
+        <v>50.628028</v>
+      </c>
+      <c r="E1102" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="1103" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1103">
+        <v>1102</v>
+      </c>
+      <c r="B1103" s="38" t="s">
+        <v>2732</v>
+      </c>
+      <c r="C1103" s="38">
+        <v>70.439344000000006</v>
+      </c>
+      <c r="D1103" s="38">
+        <v>43.179302999999997</v>
+      </c>
+      <c r="E1103" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="1104" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1104">
+        <v>1103</v>
+      </c>
+      <c r="B1104" s="38" t="s">
+        <v>2732</v>
+      </c>
+      <c r="C1104" s="38">
+        <v>69.732184166666698</v>
+      </c>
+      <c r="D1104" s="38">
+        <v>43.555528888888901</v>
+      </c>
+      <c r="E1104" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="1105" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1105">
+        <v>1104</v>
+      </c>
+      <c r="B1105" s="38" t="s">
+        <v>2732</v>
+      </c>
+      <c r="C1105" s="38">
+        <v>73.748530833333305</v>
+      </c>
+      <c r="D1105" s="38">
+        <v>43.610383333333303</v>
+      </c>
+      <c r="E1105" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="1106" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1106">
+        <v>1105</v>
+      </c>
+      <c r="B1106" s="38" t="s">
+        <v>2732</v>
+      </c>
+      <c r="C1106" s="38">
+        <v>74.707008999999999</v>
+      </c>
+      <c r="D1106" s="38">
+        <v>43.080649000000001</v>
+      </c>
+      <c r="E1106" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="1107" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1107">
+        <v>1106</v>
+      </c>
+      <c r="B1107" s="38" t="s">
+        <v>2729</v>
+      </c>
+      <c r="C1107" s="38">
+        <v>71.384587999999994</v>
+      </c>
+      <c r="D1107" s="38">
+        <v>42.921005999999998</v>
+      </c>
+      <c r="E1107" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="1108" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1108">
+        <v>1107</v>
+      </c>
+      <c r="B1108" s="38" t="s">
+        <v>2732</v>
+      </c>
+      <c r="C1108" s="38">
+        <v>71.327224444444397</v>
+      </c>
+      <c r="D1108" s="38">
+        <v>42.893129444444398</v>
+      </c>
+      <c r="E1108" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="1109" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1109">
+        <v>1108</v>
+      </c>
+      <c r="B1109" s="38" t="s">
+        <v>2739</v>
+      </c>
+      <c r="C1109" s="38">
+        <v>71.346769444444405</v>
+      </c>
+      <c r="D1109" s="38">
+        <v>42.902400277777801</v>
+      </c>
+      <c r="E1109" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="1110" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1110">
+        <v>1109</v>
+      </c>
+      <c r="B1110" s="38" t="s">
+        <v>2728</v>
+      </c>
+      <c r="C1110" s="38">
+        <v>71.380230999999995</v>
+      </c>
+      <c r="D1110" s="38">
+        <v>42.901403000000002</v>
+      </c>
+      <c r="E1110" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="1111" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1111">
+        <v>1110</v>
+      </c>
+      <c r="B1111" s="38" t="s">
+        <v>2757</v>
+      </c>
+      <c r="C1111" s="38">
+        <v>71.384619000000001</v>
+      </c>
+      <c r="D1111" s="38">
+        <v>42.877085999999998</v>
+      </c>
+      <c r="E1111" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="1112" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1112">
+        <v>1111</v>
+      </c>
+      <c r="B1112" s="38" t="s">
+        <v>2744</v>
+      </c>
+      <c r="C1112" s="38">
+        <v>52.71</v>
+      </c>
+      <c r="D1112" s="38">
+        <v>51.43</v>
+      </c>
+      <c r="E1112" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="1113" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1113">
+        <v>1112</v>
+      </c>
+      <c r="B1113" s="38" t="s">
+        <v>2757</v>
+      </c>
+      <c r="C1113" s="38">
+        <v>52.997151666666703</v>
+      </c>
+      <c r="D1113" s="38">
+        <v>51.160010277777801</v>
+      </c>
+      <c r="E1113" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="1114" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1114">
+        <v>1113</v>
+      </c>
+      <c r="B1114" s="38" t="s">
+        <v>2728</v>
+      </c>
+      <c r="C1114" s="38">
+        <v>51.348907777777796</v>
+      </c>
+      <c r="D1114" s="38">
+        <v>51.212033611111103</v>
+      </c>
+      <c r="E1114" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="1115" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1115">
+        <v>1114</v>
+      </c>
+      <c r="B1115" s="38" t="s">
+        <v>2730</v>
+      </c>
+      <c r="C1115" s="38">
+        <v>51.383433888888902</v>
+      </c>
+      <c r="D1115" s="38">
+        <v>51.205518611111103</v>
+      </c>
+      <c r="E1115" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="1116" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1116">
+        <v>1115</v>
+      </c>
+      <c r="B1116" s="38" t="s">
+        <v>2739</v>
+      </c>
+      <c r="C1116" s="38">
+        <v>51.427194722222197</v>
+      </c>
+      <c r="D1116" s="38">
+        <v>51.227171666666699</v>
+      </c>
+      <c r="E1116" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="1117" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1117">
+        <v>1116</v>
+      </c>
+      <c r="B1117" s="38" t="s">
+        <v>2729</v>
+      </c>
+      <c r="C1117" s="38">
+        <v>51.304166670000001</v>
+      </c>
+      <c r="D1117" s="38">
+        <v>51.174579999999999</v>
+      </c>
+      <c r="E1117" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="1118" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1118">
+        <v>1117</v>
+      </c>
+      <c r="B1118" s="38" t="s">
+        <v>2730</v>
+      </c>
+      <c r="C1118" s="38">
+        <v>73.168153888888895</v>
+      </c>
+      <c r="D1118" s="38">
+        <v>49.786529444444398</v>
+      </c>
+      <c r="E1118" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="1119" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1119">
+        <v>1118</v>
+      </c>
+      <c r="B1119" s="38" t="s">
+        <v>2729</v>
+      </c>
+      <c r="C1119" s="38">
+        <v>73.189188888888907</v>
+      </c>
+      <c r="D1119" s="38">
+        <v>49.878535833333302</v>
+      </c>
+      <c r="E1119" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="1120" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1120">
+        <v>1119</v>
+      </c>
+      <c r="B1120" s="38" t="s">
+        <v>2740</v>
+      </c>
+      <c r="C1120" s="38">
+        <v>73.086705555555596</v>
+      </c>
+      <c r="D1120" s="38">
+        <v>49.897955000000003</v>
+      </c>
+      <c r="E1120" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="1121" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1121">
+        <v>1120</v>
+      </c>
+      <c r="B1121" s="38" t="s">
+        <v>2732</v>
+      </c>
+      <c r="C1121" s="38">
+        <v>73.143345555555598</v>
+      </c>
+      <c r="D1121" s="38">
+        <v>49.810515000000002</v>
+      </c>
+      <c r="E1121" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="1122" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1122">
+        <v>1121</v>
+      </c>
+      <c r="B1122" s="38" t="s">
+        <v>2728</v>
+      </c>
+      <c r="C1122" s="38">
+        <v>73.080189166666699</v>
+      </c>
+      <c r="D1122" s="38">
+        <v>49.814059999999998</v>
+      </c>
+      <c r="E1122" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="1123" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1123">
+        <v>1122</v>
+      </c>
+      <c r="B1123" s="38" t="s">
+        <v>2757</v>
+      </c>
+      <c r="C1123" s="38">
+        <v>73.201671666666698</v>
+      </c>
+      <c r="D1123" s="38">
+        <v>49.890706388888901</v>
+      </c>
+      <c r="E1123" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="1124" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1124">
+        <v>1123</v>
+      </c>
+      <c r="B1124" s="38" t="s">
+        <v>2744</v>
+      </c>
+      <c r="C1124" s="38">
+        <v>73.073987500000001</v>
+      </c>
+      <c r="D1124" s="38">
+        <v>49.780421388888897</v>
+      </c>
+      <c r="E1124" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="1125" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1125">
+        <v>1124</v>
+      </c>
+      <c r="B1125" s="38" t="s">
+        <v>2732</v>
+      </c>
+      <c r="C1125" s="38">
+        <v>67.716283000000004</v>
+      </c>
+      <c r="D1125" s="38">
+        <v>47.806431000000003</v>
+      </c>
+      <c r="E1125" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="1126" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1126">
+        <v>1125</v>
+      </c>
+      <c r="B1126" s="38" t="s">
+        <v>2739</v>
+      </c>
+      <c r="C1126" s="38">
+        <v>67.690388999999996</v>
+      </c>
+      <c r="D1126" s="38">
+        <v>47.784936999999999</v>
+      </c>
+      <c r="E1126" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="1127" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1127">
+        <v>1126</v>
+      </c>
+      <c r="B1127" s="38" t="s">
+        <v>2728</v>
+      </c>
+      <c r="C1127" s="38">
+        <v>67.715261999999996</v>
+      </c>
+      <c r="D1127" s="38">
+        <v>47.792001999999997</v>
+      </c>
+      <c r="E1127" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="1128" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1128">
+        <v>1127</v>
+      </c>
+      <c r="B1128" s="38" t="s">
+        <v>2739</v>
+      </c>
+      <c r="C1128" s="38">
+        <v>72.996453611111093</v>
+      </c>
+      <c r="D1128" s="38">
+        <v>50.051492500000002</v>
+      </c>
+      <c r="E1128" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="1129" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1129">
+        <v>1128</v>
+      </c>
+      <c r="B1129" s="38" t="s">
+        <v>2728</v>
+      </c>
+      <c r="C1129" s="38">
+        <v>72.947649166666693</v>
+      </c>
+      <c r="D1129" s="38">
+        <v>50.057794444444397</v>
+      </c>
+      <c r="E1129" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="1130" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1130">
+        <v>1129</v>
+      </c>
+      <c r="B1130" s="38" t="s">
+        <v>2757</v>
+      </c>
+      <c r="C1130" s="38">
+        <v>72.953254999999999</v>
+      </c>
+      <c r="D1130" s="38">
+        <v>50.045656999999999</v>
+      </c>
+      <c r="E1130" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="1131" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1131">
+        <v>1130</v>
+      </c>
+      <c r="B1131" s="38" t="s">
+        <v>2730</v>
+      </c>
+      <c r="C1131" s="38">
+        <v>72.9561430555556</v>
+      </c>
+      <c r="D1131" s="38">
+        <v>50.065929166666699</v>
+      </c>
+      <c r="E1131" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="1132" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1132">
+        <v>1131</v>
+      </c>
+      <c r="B1132" s="38" t="s">
+        <v>2739</v>
+      </c>
+      <c r="C1132" s="38">
+        <v>74.970258888888907</v>
+      </c>
+      <c r="D1132" s="38">
+        <v>46.837768888888903</v>
+      </c>
+      <c r="E1132" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="1133" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1133">
+        <v>1132</v>
+      </c>
+      <c r="B1133" s="38" t="s">
+        <v>2732</v>
+      </c>
+      <c r="C1133" s="38">
+        <v>74.976939000000002</v>
+      </c>
+      <c r="D1133" s="38">
+        <v>46.851081000000001</v>
+      </c>
+      <c r="E1133" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="1134" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1134">
+        <v>1133</v>
+      </c>
+      <c r="B1134" s="38" t="s">
+        <v>2728</v>
+      </c>
+      <c r="C1134" s="38">
+        <v>74.975555560000004</v>
+      </c>
+      <c r="D1134" s="38">
+        <v>46.841388889999998</v>
+      </c>
+      <c r="E1134" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="1135" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1135">
+        <v>1134</v>
+      </c>
+      <c r="B1135" s="38" t="s">
+        <v>2757</v>
+      </c>
+      <c r="C1135" s="38">
+        <v>74.990305833333295</v>
+      </c>
+      <c r="D1135" s="38">
+        <v>46.837717777777797</v>
+      </c>
+      <c r="E1135" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="1136" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1136">
+        <v>1135</v>
+      </c>
+      <c r="B1136" s="38" t="s">
+        <v>2718</v>
+      </c>
+      <c r="C1136" s="38">
+        <v>72.825197777777802</v>
+      </c>
+      <c r="D1136" s="38">
+        <v>49.803393055555603</v>
+      </c>
+      <c r="E1136" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="1137" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1137">
+        <v>1136</v>
+      </c>
+      <c r="B1137" s="38" t="s">
+        <v>2719</v>
+      </c>
+      <c r="C1137" s="38">
+        <v>67.529694000000006</v>
+      </c>
+      <c r="D1137" s="38">
+        <v>47.910167000000001</v>
+      </c>
+      <c r="E1137" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="1138" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1138">
+        <v>1137</v>
+      </c>
+      <c r="B1138" s="38" t="s">
+        <v>2718</v>
+      </c>
+      <c r="C1138" s="38">
+        <v>67.547667000000004</v>
+      </c>
+      <c r="D1138" s="38">
+        <v>47.898972000000001</v>
+      </c>
+      <c r="E1138" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="1139" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1139">
+        <v>1138</v>
+      </c>
+      <c r="B1139" s="38" t="s">
+        <v>2719</v>
+      </c>
+      <c r="C1139" s="38">
+        <v>72.855277999999998</v>
+      </c>
+      <c r="D1139" s="38">
+        <v>49.633611000000002</v>
+      </c>
+      <c r="E1139" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="1140" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1140">
+        <v>1139</v>
+      </c>
+      <c r="B1140" s="38" t="s">
+        <v>2758</v>
+      </c>
+      <c r="C1140" s="38">
+        <v>62.053193333333297</v>
+      </c>
+      <c r="D1140" s="38">
+        <v>53.748925</v>
+      </c>
+      <c r="E1140" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="1141" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1141">
+        <v>1140</v>
+      </c>
+      <c r="B1141" s="38" t="s">
+        <v>2739</v>
+      </c>
+      <c r="C1141" s="38">
+        <v>63.630640555555601</v>
+      </c>
+      <c r="D1141" s="38">
+        <v>53.228382222222201</v>
+      </c>
+      <c r="E1141" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="1142" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1142">
+        <v>1141</v>
+      </c>
+      <c r="B1142" s="38" t="s">
+        <v>2757</v>
+      </c>
+      <c r="C1142" s="38">
+        <v>63.607446944444398</v>
+      </c>
+      <c r="D1142" s="38">
+        <v>53.176315277777803</v>
+      </c>
+      <c r="E1142" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="1143" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1143">
+        <v>1142</v>
+      </c>
+      <c r="B1143" s="38" t="s">
+        <v>2732</v>
+      </c>
+      <c r="C1143" s="38">
+        <v>63.679906666666703</v>
+      </c>
+      <c r="D1143" s="38">
+        <v>53.239156944444403</v>
+      </c>
+      <c r="E1143" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="1144" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1144">
+        <v>1143</v>
+      </c>
+      <c r="B1144" s="38" t="s">
+        <v>2728</v>
+      </c>
+      <c r="C1144" s="38">
+        <v>63.622039722222198</v>
+      </c>
+      <c r="D1144" s="38">
+        <v>53.209909444444399</v>
+      </c>
+      <c r="E1144" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="1145" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1145">
+        <v>1144</v>
+      </c>
+      <c r="B1145" s="38" t="s">
+        <v>2729</v>
+      </c>
+      <c r="C1145" s="38">
+        <v>63.114155277777797</v>
+      </c>
+      <c r="D1145" s="38">
+        <v>52.964545000000001</v>
+      </c>
+      <c r="E1145" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="1146" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1146">
+        <v>1145</v>
+      </c>
+      <c r="B1146" s="38" t="s">
+        <v>2730</v>
+      </c>
+      <c r="C1146" s="38">
+        <v>63.123032500000001</v>
+      </c>
+      <c r="D1146" s="38">
+        <v>52.973584444444398</v>
+      </c>
+      <c r="E1146" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="1147" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1147">
+        <v>1146</v>
+      </c>
+      <c r="B1147" s="38" t="s">
+        <v>2719</v>
+      </c>
+      <c r="C1147" s="38">
+        <v>62.494833</v>
+      </c>
+      <c r="D1147" s="38">
+        <v>52.547556</v>
+      </c>
+      <c r="E1147" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="1148" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1148">
+        <v>1147</v>
+      </c>
+      <c r="B1148" s="38" t="s">
+        <v>2719</v>
+      </c>
+      <c r="C1148" s="38">
+        <v>66.921222</v>
+      </c>
+      <c r="D1148" s="38">
+        <v>50.249056000000003</v>
+      </c>
+      <c r="E1148" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="1149" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1149">
+        <v>1148</v>
+      </c>
+      <c r="B1149" s="38" t="s">
+        <v>2719</v>
+      </c>
+      <c r="C1149" s="38">
+        <v>61.198028000000001</v>
+      </c>
+      <c r="D1149" s="38">
+        <v>52.189222000000001</v>
+      </c>
+      <c r="E1149" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="1150" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1150">
+        <v>1149</v>
+      </c>
+      <c r="B1150" s="38" t="s">
+        <v>2739</v>
+      </c>
+      <c r="C1150" s="38">
+        <v>65.486898109812699</v>
+      </c>
+      <c r="D1150" s="38">
+        <v>44.847024260780003</v>
+      </c>
+      <c r="E1150" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="1151" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1151">
+        <v>1150</v>
+      </c>
+      <c r="B1151" s="38" t="s">
+        <v>2728</v>
+      </c>
+      <c r="C1151" s="38">
+        <v>65.530045998381894</v>
+      </c>
+      <c r="D1151" s="38">
+        <v>44.794852996375802</v>
+      </c>
+      <c r="E1151" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="1152" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1152">
+        <v>1151</v>
+      </c>
+      <c r="B1152" s="38" t="s">
+        <v>2732</v>
+      </c>
+      <c r="C1152" s="38">
+        <v>65.525356775125005</v>
+      </c>
+      <c r="D1152" s="38">
+        <v>44.839062404083897</v>
+      </c>
+      <c r="E1152" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="1153" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1153">
+        <v>1152</v>
+      </c>
+      <c r="B1153" s="38" t="s">
+        <v>2732</v>
+      </c>
+      <c r="C1153" s="38">
+        <v>63.305771</v>
+      </c>
+      <c r="D1153" s="38">
+        <v>45.644193000000001</v>
+      </c>
+      <c r="E1153" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="1154" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1154">
+        <v>1153</v>
+      </c>
+      <c r="B1154" s="38" t="s">
+        <v>2732</v>
+      </c>
+      <c r="C1154" s="38">
+        <v>63.281641999999998</v>
+      </c>
+      <c r="D1154" s="38">
+        <v>45.610717999999999</v>
+      </c>
+      <c r="E1154" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="1155" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1155">
+        <v>1154</v>
+      </c>
+      <c r="B1155" s="38" t="s">
+        <v>2719</v>
+      </c>
+      <c r="C1155" s="38">
+        <v>62.138193999999999</v>
+      </c>
+      <c r="D1155" s="38">
+        <v>45.827528000000001</v>
+      </c>
+      <c r="E1155" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="1156" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1156">
+        <v>1155</v>
+      </c>
+      <c r="B1156" s="38" t="s">
+        <v>2719</v>
+      </c>
+      <c r="C1156" s="38">
+        <v>66.729472000000001</v>
+      </c>
+      <c r="D1156" s="38">
+        <v>44.196944000000002</v>
+      </c>
+      <c r="E1156" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="1157" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1157">
+        <v>1156</v>
+      </c>
+      <c r="B1157" s="38" t="s">
+        <v>2719</v>
+      </c>
+      <c r="C1157" s="38">
+        <v>61.646472000000003</v>
+      </c>
+      <c r="D1157" s="38">
+        <v>46.808667</v>
+      </c>
+      <c r="E1157" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="1158" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1158">
+        <v>1157</v>
+      </c>
+      <c r="B1158" s="38" t="s">
+        <v>2717</v>
+      </c>
+      <c r="C1158" s="38">
+        <v>51.1709258333333</v>
+      </c>
+      <c r="D1158" s="38">
+        <v>43.678626944444403</v>
+      </c>
+      <c r="E1158" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="1159" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1159">
+        <v>1158</v>
+      </c>
+      <c r="B1159" s="38" t="s">
+        <v>2722</v>
+      </c>
+      <c r="C1159" s="38">
+        <v>51.147579722222197</v>
+      </c>
+      <c r="D1159" s="38">
+        <v>43.658270277777802</v>
+      </c>
+      <c r="E1159" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="1160" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1160">
+        <v>1159</v>
+      </c>
+      <c r="B1160" s="38" t="s">
+        <v>2720</v>
+      </c>
+      <c r="C1160" s="38">
+        <v>51.178227</v>
+      </c>
+      <c r="D1160" s="38">
+        <v>43.632686999999997</v>
+      </c>
+      <c r="E1160" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="1161" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1161">
+        <v>1160</v>
+      </c>
+      <c r="B1161" s="38" t="s">
+        <v>2721</v>
+      </c>
+      <c r="C1161" s="38">
+        <v>51.174962999999998</v>
+      </c>
+      <c r="D1161" s="38">
+        <v>43.644471000000003</v>
+      </c>
+      <c r="E1161" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="1162" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1162">
+        <v>1161</v>
+      </c>
+      <c r="B1162" s="38" t="s">
+        <v>2744</v>
+      </c>
+      <c r="C1162" s="38">
+        <v>55.178201944444403</v>
+      </c>
+      <c r="D1162" s="38">
+        <v>45.323396666666703</v>
+      </c>
+      <c r="E1162" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="1163" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1163">
+        <v>1162</v>
+      </c>
+      <c r="B1163" s="38" t="s">
+        <v>2739</v>
+      </c>
+      <c r="C1163" s="38">
+        <v>52.846829722222203</v>
+      </c>
+      <c r="D1163" s="38">
+        <v>43.350638055555599</v>
+      </c>
+      <c r="E1163" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="1164" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1164">
+        <v>1163</v>
+      </c>
+      <c r="B1164" s="38" t="s">
+        <v>2732</v>
+      </c>
+      <c r="C1164" s="38">
+        <v>52.854202999999998</v>
+      </c>
+      <c r="D1164" s="38">
+        <v>43.340533000000001</v>
+      </c>
+      <c r="E1164" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="1165" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1165">
+        <v>1164</v>
+      </c>
+      <c r="B1165" s="38" t="s">
+        <v>2730</v>
+      </c>
+      <c r="C1165" s="38">
+        <v>76.946049722222199</v>
+      </c>
+      <c r="D1165" s="38">
+        <v>52.281144722222201</v>
+      </c>
+      <c r="E1165" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="1166" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1166">
+        <v>1165</v>
+      </c>
+      <c r="B1166" s="38" t="s">
+        <v>2729</v>
+      </c>
+      <c r="C1166" s="38">
+        <v>76.937730555555603</v>
+      </c>
+      <c r="D1166" s="38">
+        <v>52.265217222222198</v>
+      </c>
+      <c r="E1166" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="1167" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1167">
+        <v>1166</v>
+      </c>
+      <c r="B1167" s="38" t="s">
+        <v>2744</v>
+      </c>
+      <c r="C1167" s="38">
+        <v>76.942828333333296</v>
+      </c>
+      <c r="D1167" s="38">
+        <v>52.294865277777802</v>
+      </c>
+      <c r="E1167" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="1168" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1168">
+        <v>1167</v>
+      </c>
+      <c r="B1168" s="38" t="s">
+        <v>2757</v>
+      </c>
+      <c r="C1168" s="38">
+        <v>76.982703055555604</v>
+      </c>
+      <c r="D1168" s="38">
+        <v>52.246117222222203</v>
+      </c>
+      <c r="E1168" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="1169" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1169">
+        <v>1168</v>
+      </c>
+      <c r="B1169" s="38" t="s">
+        <v>2728</v>
+      </c>
+      <c r="C1169" s="38">
+        <v>76.964077500000002</v>
+      </c>
+      <c r="D1169" s="38">
+        <v>52.2647030555556</v>
+      </c>
+      <c r="E1169" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="1170" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1170">
+        <v>1169</v>
+      </c>
+      <c r="B1170" s="38" t="s">
+        <v>2732</v>
+      </c>
+      <c r="C1170" s="38">
+        <v>76.980948888888904</v>
+      </c>
+      <c r="D1170" s="38">
+        <v>52.298005833333299</v>
+      </c>
+      <c r="E1170" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="1171" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1171">
+        <v>1170</v>
+      </c>
+      <c r="B1171" s="38" t="s">
+        <v>2739</v>
+      </c>
+      <c r="C1171" s="38">
+        <v>76.917159444444493</v>
+      </c>
+      <c r="D1171" s="38">
+        <v>52.2994363888889</v>
+      </c>
+      <c r="E1171" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="1172" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1172">
+        <v>1171</v>
+      </c>
+      <c r="B1172" s="38" t="s">
+        <v>2732</v>
+      </c>
+      <c r="C1172" s="38">
+        <v>75.331964444444495</v>
+      </c>
+      <c r="D1172" s="38">
+        <v>51.711341944444399</v>
+      </c>
+      <c r="E1172" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="1173" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1173">
+        <v>1172</v>
+      </c>
+      <c r="B1173" s="38" t="s">
+        <v>2739</v>
+      </c>
+      <c r="C1173" s="38">
+        <v>75.308875277777801</v>
+      </c>
+      <c r="D1173" s="38">
+        <v>51.716758888888897</v>
+      </c>
+      <c r="E1173" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="1174" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1174">
+        <v>1173</v>
+      </c>
+      <c r="B1174" s="38" t="s">
+        <v>2732</v>
+      </c>
+      <c r="C1174" s="38">
+        <v>76.920432777777805</v>
+      </c>
+      <c r="D1174" s="38">
+        <v>52.039080277777799</v>
+      </c>
+      <c r="E1174" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="1175" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1175">
+        <v>1174</v>
+      </c>
+      <c r="B1175" s="38" t="s">
+        <v>2729</v>
+      </c>
+      <c r="C1175" s="38">
+        <v>69.141182999999998</v>
+      </c>
+      <c r="D1175" s="38">
+        <v>54.923251999999998</v>
+      </c>
+      <c r="E1175" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="1176" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1176">
+        <v>1175</v>
+      </c>
+      <c r="B1176" s="38" t="s">
+        <v>2730</v>
+      </c>
+      <c r="C1176" s="38">
+        <v>69.123301999999995</v>
+      </c>
+      <c r="D1176" s="38">
+        <v>54.856878000000002</v>
+      </c>
+      <c r="E1176" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="1177" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1177">
+        <v>1176</v>
+      </c>
+      <c r="B1177" s="38" t="s">
+        <v>2732</v>
+      </c>
+      <c r="C1177" s="38">
+        <v>69.143214999999998</v>
+      </c>
+      <c r="D1177" s="38">
+        <v>54.899923000000001</v>
+      </c>
+      <c r="E1177" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="1178" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1178">
+        <v>1177</v>
+      </c>
+      <c r="B1178" s="38" t="s">
+        <v>2728</v>
+      </c>
+      <c r="C1178" s="38">
+        <v>69.132626000000002</v>
+      </c>
+      <c r="D1178" s="38">
+        <v>54.872523999999999</v>
+      </c>
+      <c r="E1178" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="1179" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1179">
+        <v>1178</v>
+      </c>
+      <c r="B1179" s="38" t="s">
+        <v>2717</v>
+      </c>
+      <c r="C1179" s="38">
+        <v>69.629853999999995</v>
+      </c>
+      <c r="D1179" s="38">
+        <v>42.358319000000002</v>
+      </c>
+      <c r="E1179" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="1180" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1180">
+        <v>1179</v>
+      </c>
+      <c r="B1180" s="38" t="s">
+        <v>2722</v>
+      </c>
+      <c r="C1180" s="38">
+        <v>69.593401999999998</v>
+      </c>
+      <c r="D1180" s="38">
+        <v>42.362152000000002</v>
+      </c>
+      <c r="E1180" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="1181" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1181">
+        <v>1180</v>
+      </c>
+      <c r="B1181" s="38" t="s">
+        <v>2719</v>
+      </c>
+      <c r="C1181" s="38">
+        <v>69.566805000000002</v>
+      </c>
+      <c r="D1181" s="38">
+        <v>42.320965000000001</v>
+      </c>
+      <c r="E1181" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="1182" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1182">
+        <v>1181</v>
+      </c>
+      <c r="B1182" s="38" t="s">
+        <v>2718</v>
+      </c>
+      <c r="C1182" s="38">
+        <v>69.600329166666697</v>
+      </c>
+      <c r="D1182" s="38">
+        <v>42.309648611111101</v>
+      </c>
+      <c r="E1182" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="1183" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1183">
+        <v>1182</v>
+      </c>
+      <c r="B1183" s="38" t="s">
+        <v>2720</v>
+      </c>
+      <c r="C1183" s="38">
+        <v>69.625827000000001</v>
+      </c>
+      <c r="D1183" s="38">
+        <v>42.305453999999997</v>
+      </c>
+      <c r="E1183" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="1184" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1184">
+        <v>1183</v>
+      </c>
+      <c r="B1184" s="38" t="s">
+        <v>2715</v>
+      </c>
+      <c r="C1184" s="38">
+        <v>69.645844999999994</v>
+      </c>
+      <c r="D1184" s="38">
+        <v>42.330120999999998</v>
+      </c>
+      <c r="E1184" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="1185" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1185">
+        <v>1184</v>
+      </c>
+      <c r="B1185" s="38" t="s">
+        <v>2732</v>
+      </c>
+      <c r="C1185" s="38">
+        <v>68.487763000000001</v>
+      </c>
+      <c r="D1185" s="38">
+        <v>43.513666999999998</v>
+      </c>
+      <c r="E1185" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="1186" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1186">
+        <v>1185</v>
+      </c>
+      <c r="B1186" s="38" t="s">
+        <v>2732</v>
+      </c>
+      <c r="C1186" s="38">
+        <v>68.305418000000003</v>
+      </c>
+      <c r="D1186" s="38">
+        <v>43.286344999999997</v>
+      </c>
+      <c r="E1186" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="1187" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1187">
+        <v>1186</v>
+      </c>
+      <c r="B1187" s="38" t="s">
+        <v>2720</v>
+      </c>
+      <c r="C1187" s="38">
+        <v>68.203305999999998</v>
+      </c>
+      <c r="D1187" s="38">
+        <v>43.278222</v>
+      </c>
+      <c r="E1187" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="1188" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1188">
+        <v>1187</v>
+      </c>
+      <c r="B1188" s="38" t="s">
+        <v>2718</v>
+      </c>
+      <c r="C1188" s="38">
+        <v>68.289556000000005</v>
+      </c>
+      <c r="D1188" s="38">
+        <v>43.293388999999998</v>
+      </c>
+      <c r="E1188" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="1189" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1189">
+        <v>1188</v>
+      </c>
+      <c r="B1189" s="38" t="s">
+        <v>2721</v>
+      </c>
+      <c r="C1189" s="38">
+        <v>69.709999999999994</v>
+      </c>
+      <c r="D1189" s="38">
+        <v>42.347777999999998</v>
+      </c>
+      <c r="E1189" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="1190" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1190">
+        <v>1189</v>
+      </c>
+      <c r="B1190" s="38" t="s">
+        <v>2719</v>
+      </c>
+      <c r="C1190" s="38">
+        <v>70.006693999999996</v>
+      </c>
+      <c r="D1190" s="38">
+        <v>42.551833000000002</v>
+      </c>
+      <c r="E1190" t="s">
+        <v>2723</v>
       </c>
     </row>
   </sheetData>

--- a/station.xlsx
+++ b/station.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\eltai_a\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75C1EB8C-E4AA-44B1-A29A-E9F55D46ADE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED4FE041-E00C-410F-A36E-0F9BA6B931CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13001" yWindow="177" windowWidth="22958" windowHeight="18828" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="12063" yWindow="14" windowWidth="22959" windowHeight="18828" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3278" uniqueCount="1937">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3269" uniqueCount="1928">
   <si>
     <t>Станция/пост</t>
   </si>
@@ -5877,33 +5877,6 @@
     <t>ПНЗ№7</t>
   </si>
   <si>
-    <t xml:space="preserve">46.953111° </t>
-  </si>
-  <si>
-    <t>51.735194°</t>
-  </si>
-  <si>
-    <t>47.094444°</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 51.891361°</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.083333° </t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.9° </t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.133333° </t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.866667° </t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.933333° </t>
-  </si>
-  <si>
     <t xml:space="preserve">53.983333° </t>
   </si>
   <si>
@@ -5926,12 +5899,20 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -6134,138 +6115,139 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -6563,7 +6545,7 @@
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>1936</v>
+        <v>1927</v>
       </c>
       <c r="D1" t="s">
         <v>1</v>
@@ -24698,11 +24680,11 @@
       <c r="B1068" s="38" t="s">
         <v>1919</v>
       </c>
-      <c r="C1068" s="38" t="s">
-        <v>1923</v>
-      </c>
-      <c r="D1068" s="38" t="s">
-        <v>1922</v>
+      <c r="C1068" s="38">
+        <v>51.735194</v>
+      </c>
+      <c r="D1068" s="38">
+        <v>46.953111</v>
       </c>
       <c r="E1068" t="s">
         <v>1900</v>
@@ -24715,11 +24697,11 @@
       <c r="B1069" s="38" t="s">
         <v>1910</v>
       </c>
-      <c r="C1069" s="38" t="s">
-        <v>1925</v>
-      </c>
-      <c r="D1069" s="38" t="s">
-        <v>1924</v>
+      <c r="C1069" s="38">
+        <v>51.891361000000003</v>
+      </c>
+      <c r="D1069" s="38">
+        <v>47.094444000000003</v>
       </c>
       <c r="E1069" t="s">
         <v>1900</v>
@@ -24732,11 +24714,11 @@
       <c r="B1070" s="38" t="s">
         <v>1907</v>
       </c>
-      <c r="C1070" s="38" t="s">
-        <v>1927</v>
-      </c>
-      <c r="D1070" s="38" t="s">
-        <v>1926</v>
+      <c r="C1070" s="49">
+        <v>51.9</v>
+      </c>
+      <c r="D1070" s="38">
+        <v>47.083333000000003</v>
       </c>
       <c r="E1070" t="s">
         <v>1900</v>
@@ -24749,11 +24731,11 @@
       <c r="B1071" s="38" t="s">
         <v>1920</v>
       </c>
-      <c r="C1071" s="38" t="s">
-        <v>1929</v>
-      </c>
-      <c r="D1071" s="38" t="s">
-        <v>1928</v>
+      <c r="C1071" s="38">
+        <v>51.866667</v>
+      </c>
+      <c r="D1071" s="38">
+        <v>47.133333</v>
       </c>
       <c r="E1071" t="s">
         <v>1900</v>
@@ -24818,10 +24800,10 @@
         <v>1921</v>
       </c>
       <c r="C1075" s="38" t="s">
-        <v>1931</v>
-      </c>
-      <c r="D1075" s="38" t="s">
-        <v>1930</v>
+        <v>1922</v>
+      </c>
+      <c r="D1075" s="38">
+        <v>46.933332999999998</v>
       </c>
       <c r="E1075" t="s">
         <v>1900</v>
@@ -25104,7 +25086,7 @@
         <v>1091</v>
       </c>
       <c r="B1092" s="38" t="s">
-        <v>1932</v>
+        <v>1923</v>
       </c>
       <c r="C1092" s="38">
         <v>49.900071944444399</v>
@@ -25155,7 +25137,7 @@
         <v>1094</v>
       </c>
       <c r="B1095" s="38" t="s">
-        <v>1933</v>
+        <v>1924</v>
       </c>
       <c r="C1095" s="38">
         <v>49.900888999999999</v>
@@ -25427,7 +25409,7 @@
         <v>1110</v>
       </c>
       <c r="B1111" s="38" t="s">
-        <v>1934</v>
+        <v>1925</v>
       </c>
       <c r="C1111" s="38">
         <v>42.877085999999998</v>
@@ -25461,7 +25443,7 @@
         <v>1112</v>
       </c>
       <c r="B1113" s="38" t="s">
-        <v>1934</v>
+        <v>1925</v>
       </c>
       <c r="C1113" s="38">
         <v>51.160010277777801</v>
@@ -25631,7 +25613,7 @@
         <v>1122</v>
       </c>
       <c r="B1123" s="38" t="s">
-        <v>1934</v>
+        <v>1925</v>
       </c>
       <c r="C1123" s="38">
         <v>49.890706388888901</v>
@@ -25750,7 +25732,7 @@
         <v>1129</v>
       </c>
       <c r="B1130" s="38" t="s">
-        <v>1934</v>
+        <v>1925</v>
       </c>
       <c r="C1130" s="38">
         <v>50.045656999999999</v>
@@ -25835,7 +25817,7 @@
         <v>1134</v>
       </c>
       <c r="B1135" s="38" t="s">
-        <v>1934</v>
+        <v>1925</v>
       </c>
       <c r="C1135" s="38">
         <v>46.837717777777797</v>
@@ -25920,7 +25902,7 @@
         <v>1139</v>
       </c>
       <c r="B1140" s="38" t="s">
-        <v>1935</v>
+        <v>1926</v>
       </c>
       <c r="C1140" s="38">
         <v>53.748925</v>
@@ -25954,7 +25936,7 @@
         <v>1141</v>
       </c>
       <c r="B1142" s="38" t="s">
-        <v>1934</v>
+        <v>1925</v>
       </c>
       <c r="C1142" s="38">
         <v>53.176315277777803</v>
@@ -26396,7 +26378,7 @@
         <v>1167</v>
       </c>
       <c r="B1168" s="38" t="s">
-        <v>1934</v>
+        <v>1925</v>
       </c>
       <c r="C1168" s="38">
         <v>52.246117222222203</v>

--- a/station.xlsx
+++ b/station.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\eltai_a\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED4FE041-E00C-410F-A36E-0F9BA6B931CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06804549-0FBD-4528-B69C-EB828CC5F463}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12063" yWindow="14" windowWidth="22959" windowHeight="18828" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11819" yWindow="14" windowWidth="22958" windowHeight="18828" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -6115,7 +6115,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -6247,7 +6247,8 @@
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -24677,16 +24678,16 @@
       <c r="A1068">
         <v>1067</v>
       </c>
-      <c r="B1068" s="38" t="s">
+      <c r="B1068" s="49" t="s">
         <v>1919</v>
       </c>
-      <c r="C1068" s="38">
+      <c r="C1068" s="49">
+        <v>46.953111</v>
+      </c>
+      <c r="D1068" s="49">
         <v>51.735194</v>
       </c>
-      <c r="D1068" s="38">
-        <v>46.953111</v>
-      </c>
-      <c r="E1068" t="s">
+      <c r="E1068" s="36" t="s">
         <v>1900</v>
       </c>
     </row>
@@ -24694,16 +24695,16 @@
       <c r="A1069">
         <v>1068</v>
       </c>
-      <c r="B1069" s="38" t="s">
+      <c r="B1069" s="49" t="s">
         <v>1910</v>
       </c>
-      <c r="C1069" s="38">
+      <c r="C1069" s="49">
+        <v>47.094444000000003</v>
+      </c>
+      <c r="D1069" s="49">
         <v>51.891361000000003</v>
       </c>
-      <c r="D1069" s="38">
-        <v>47.094444000000003</v>
-      </c>
-      <c r="E1069" t="s">
+      <c r="E1069" s="36" t="s">
         <v>1900</v>
       </c>
     </row>
@@ -24711,16 +24712,16 @@
       <c r="A1070">
         <v>1069</v>
       </c>
-      <c r="B1070" s="38" t="s">
+      <c r="B1070" s="49" t="s">
         <v>1907</v>
       </c>
       <c r="C1070" s="49">
+        <v>47.083333000000003</v>
+      </c>
+      <c r="D1070" s="50">
         <v>51.9</v>
       </c>
-      <c r="D1070" s="38">
-        <v>47.083333000000003</v>
-      </c>
-      <c r="E1070" t="s">
+      <c r="E1070" s="36" t="s">
         <v>1900</v>
       </c>
     </row>
@@ -24728,16 +24729,16 @@
       <c r="A1071">
         <v>1070</v>
       </c>
-      <c r="B1071" s="38" t="s">
+      <c r="B1071" s="49" t="s">
         <v>1920</v>
       </c>
-      <c r="C1071" s="38">
+      <c r="C1071" s="49">
+        <v>47.133333</v>
+      </c>
+      <c r="D1071" s="49">
         <v>51.866667</v>
       </c>
-      <c r="D1071" s="38">
-        <v>47.133333</v>
-      </c>
-      <c r="E1071" t="s">
+      <c r="E1071" s="36" t="s">
         <v>1900</v>
       </c>
     </row>

--- a/station.xlsx
+++ b/station.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\eltai_a\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06804549-0FBD-4528-B69C-EB828CC5F463}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93C4A09E-D936-4892-99E0-6D0061F6FC07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="11819" yWindow="14" windowWidth="22958" windowHeight="18828" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3269" uniqueCount="1928">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3268" uniqueCount="1927">
   <si>
     <t>Станция/пост</t>
   </si>
@@ -5875,9 +5875,6 @@
   </si>
   <si>
     <t>ПНЗ№7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.983333° </t>
   </si>
   <si>
     <t>ПНЗ №12</t>
@@ -6546,7 +6543,7 @@
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>1927</v>
+        <v>1926</v>
       </c>
       <c r="D1" t="s">
         <v>1</v>
@@ -24800,8 +24797,8 @@
       <c r="B1075" s="38" t="s">
         <v>1921</v>
       </c>
-      <c r="C1075" s="38" t="s">
-        <v>1922</v>
+      <c r="C1075" s="38">
+        <v>53.983333000000002</v>
       </c>
       <c r="D1075" s="38">
         <v>46.933332999999998</v>
@@ -25087,7 +25084,7 @@
         <v>1091</v>
       </c>
       <c r="B1092" s="38" t="s">
-        <v>1923</v>
+        <v>1922</v>
       </c>
       <c r="C1092" s="38">
         <v>49.900071944444399</v>
@@ -25138,7 +25135,7 @@
         <v>1094</v>
       </c>
       <c r="B1095" s="38" t="s">
-        <v>1924</v>
+        <v>1923</v>
       </c>
       <c r="C1095" s="38">
         <v>49.900888999999999</v>
@@ -25410,7 +25407,7 @@
         <v>1110</v>
       </c>
       <c r="B1111" s="38" t="s">
-        <v>1925</v>
+        <v>1924</v>
       </c>
       <c r="C1111" s="38">
         <v>42.877085999999998</v>
@@ -25444,7 +25441,7 @@
         <v>1112</v>
       </c>
       <c r="B1113" s="38" t="s">
-        <v>1925</v>
+        <v>1924</v>
       </c>
       <c r="C1113" s="38">
         <v>51.160010277777801</v>
@@ -25614,7 +25611,7 @@
         <v>1122</v>
       </c>
       <c r="B1123" s="38" t="s">
-        <v>1925</v>
+        <v>1924</v>
       </c>
       <c r="C1123" s="38">
         <v>49.890706388888901</v>
@@ -25733,7 +25730,7 @@
         <v>1129</v>
       </c>
       <c r="B1130" s="38" t="s">
-        <v>1925</v>
+        <v>1924</v>
       </c>
       <c r="C1130" s="38">
         <v>50.045656999999999</v>
@@ -25818,7 +25815,7 @@
         <v>1134</v>
       </c>
       <c r="B1135" s="38" t="s">
-        <v>1925</v>
+        <v>1924</v>
       </c>
       <c r="C1135" s="38">
         <v>46.837717777777797</v>
@@ -25903,7 +25900,7 @@
         <v>1139</v>
       </c>
       <c r="B1140" s="38" t="s">
-        <v>1926</v>
+        <v>1925</v>
       </c>
       <c r="C1140" s="38">
         <v>53.748925</v>
@@ -25937,7 +25934,7 @@
         <v>1141</v>
       </c>
       <c r="B1142" s="38" t="s">
-        <v>1925</v>
+        <v>1924</v>
       </c>
       <c r="C1142" s="38">
         <v>53.176315277777803</v>
@@ -26379,7 +26376,7 @@
         <v>1167</v>
       </c>
       <c r="B1168" s="38" t="s">
-        <v>1925</v>
+        <v>1924</v>
       </c>
       <c r="C1168" s="38">
         <v>52.246117222222203</v>

--- a/station.xlsx
+++ b/station.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\eltai_a\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93C4A09E-D936-4892-99E0-6D0061F6FC07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFAEFD81-ED45-4604-97CD-BE35E36AA265}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="11819" yWindow="14" windowWidth="22958" windowHeight="18828" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25427,10 +25427,10 @@
         <v>1921</v>
       </c>
       <c r="C1112" s="38">
+        <v>52.71</v>
+      </c>
+      <c r="D1112" s="38">
         <v>51.43</v>
-      </c>
-      <c r="D1112" s="38">
-        <v>52.71</v>
       </c>
       <c r="E1112" t="s">
         <v>1900</v>

--- a/station.xlsx
+++ b/station.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\eltai_a\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFAEFD81-ED45-4604-97CD-BE35E36AA265}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{132AF29E-C403-4AEE-AE3A-58A2AF620B05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="11819" yWindow="14" windowWidth="22958" windowHeight="18828" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24781,10 +24781,10 @@
         <v>1921</v>
       </c>
       <c r="C1074" s="38">
+        <v>54.011666669999997</v>
+      </c>
+      <c r="D1074" s="38">
         <v>46.960619440000002</v>
-      </c>
-      <c r="D1074" s="38">
-        <v>54.011666669999997</v>
       </c>
       <c r="E1074" t="s">
         <v>1900</v>
@@ -25427,10 +25427,10 @@
         <v>1921</v>
       </c>
       <c r="C1112" s="38">
+        <v>51.43</v>
+      </c>
+      <c r="D1112" s="38">
         <v>52.71</v>
-      </c>
-      <c r="D1112" s="38">
-        <v>51.43</v>
       </c>
       <c r="E1112" t="s">
         <v>1900</v>

--- a/station.xlsx
+++ b/station.xlsx
@@ -24805,10 +24805,10 @@
         <v>1920</v>
       </c>
       <c r="C1075" s="38">
+        <v>46.933332999999998</v>
+      </c>
+      <c r="D1075" s="38">
         <v>53.983333000000002</v>
-      </c>
-      <c r="D1075" s="38">
-        <v>46.933332999999998</v>
       </c>
       <c r="E1075" t="s">
         <v>1899</v>
